--- a/templates/input_template.xlsx
+++ b/templates/input_template.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -532,103 +532,120 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Geburtsjahr</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1968</v>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>rainier@example.com</t>
+        </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Vierstellig, z.B. 1985</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Geschlecht</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
+          <t>Geburtsjahr</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1968</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>m | w | d (optional)</t>
+          <t>Vierstellig, z.B. 1985 — optional (kann leer bleiben)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Gewicht (kg)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>71.5</v>
+          <t>Geschlecht</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>m | w | d (optional)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Größe (m)</t>
+          <t>Gewicht (kg)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>In Metern, z.B. 1.79</t>
-        </is>
+        <v>71.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Trainingsziel</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Marathonzeit verbessern</t>
+          <t>Größe (m)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>In Metern, z.B. 1.79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Wettkampfziel</t>
+          <t>Trainingsziel</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Achenseelauf 2024</t>
+          <t>Marathonzeit verbessern</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Trainingsumfang/Woche</t>
+          <t>Wettkampfziel</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ca. 8h</t>
+          <t>Achenseelauf 2024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Trainingsumfang/Woche</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ca. 8h</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Leistungsniveau</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Hobbyläufer</t>
         </is>
@@ -645,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -700,7 +717,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Format: HH:MM</t>
+          <t>Format: hh:mm</t>
         </is>
       </c>
     </row>
@@ -743,7 +760,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Anfangsintensität</t>
+          <t>Anfangsbelastung</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -861,6 +878,32 @@
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t>JA oder NEIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Nachbelastungslaktat 3min (mmol/l)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Optional — Laktatwert 3 min nach Belastung</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Nachbelastungslaktat 5min (mmol/l)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Optional — Laktatwert 5 min nach Belastung</t>
         </is>
       </c>
     </row>

--- a/templates/input_template.xlsx
+++ b/templates/input_template.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -491,161 +491,144 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sportart</t>
+          <t>Vorname</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Lauf</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Erlaubt: lauf | rad | triathlon-rad | triathlon-lauf | unspezifisch</t>
+          <t>Rainier</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Vorname</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Rainier</t>
+          <t>Matzinger</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Matzinger</t>
+          <t>rainier@example.com</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>rainier@example.com</t>
-        </is>
+          <t>Geburtsjahr</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1968</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Vierstellig, z.B. 1985 — optional (kann leer bleiben)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Geburtsjahr</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1968</v>
+          <t>Geschlecht</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Vierstellig, z.B. 1985 — optional (kann leer bleiben)</t>
+          <t>m | w | d (optional)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Geschlecht</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>m | w | d (optional)</t>
-        </is>
+          <t>Gewicht (kg)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>71.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Gewicht (kg)</t>
+          <t>Größe (m)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>71.5</v>
+        <v>1.79</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>In Metern, z.B. 1.79</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Größe (m)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>In Metern, z.B. 1.79</t>
+          <t>Trainingsziel</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Marathonzeit verbessern</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Trainingsziel</t>
+          <t>Wettkampfziel</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Marathonzeit verbessern</t>
+          <t>Achenseelauf 2024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Wettkampfziel</t>
+          <t>Trainingsumfang/Woche</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Achenseelauf 2024</t>
+          <t>ca. 8h</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Trainingsumfang/Woche</t>
+          <t>Leistungsniveau</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ca. 8h</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Leistungsniveau</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Hobbyläufer</t>
         </is>
@@ -662,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -690,218 +673,235 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Testdatum</t>
+          <t>Sportart</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>23.05.2024</t>
+          <t>Lauf</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Format: TT.MM.JJJJ</t>
+          <t>Erlaubt: lauf | rad | triathlon-rad | triathlon-lauf | unspezifisch</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Uhrzeit</t>
+          <t>Testdatum</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23.05.2024</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Format: hh:mm</t>
+          <t>Format: TT.MM.JJJJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Durchführungsort</t>
+          <t>Uhrzeit</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Laufcamp Achensee</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Format: hh:mm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Testleiter</t>
+          <t>Durchführungsort</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Anna-Maria Wörndle</t>
+          <t>Laufcamp Achensee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Gerät</t>
+          <t>Testleiter</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Laufband Atoll Achensee</t>
+          <t>Anna-Maria Wörndle</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Anfangsbelastung</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>km/h (Lauf) | W (Rad) | Stufe (Unspez)</t>
+          <t>Gerät</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Laufband Atoll Achensee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Stufeninkrement</t>
+          <t>Anfangsbelastung</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>km/h | W | Stufen</t>
+          <t>km/h (Lauf) | W (Rad) | Stufe (Unspez)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Stufendauer (min)</t>
+          <t>Stufeninkrement</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Minuten</t>
+          <t>km/h | W | Stufen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Stufenlänge (m)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
+          <t>Stufendauer (min)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Optional, nur Lauf (z.B. 1600)</t>
+          <t>Minuten</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Besonderheiten</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>1% Steigung</t>
-        </is>
-      </c>
+          <t>Stufenlänge (m)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Freitext</t>
+          <t>Optional, nur Lauf (z.B. 1600)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Letzte Stufe vollständig absolviert</t>
+          <t>Besonderheiten</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>1% Steigung</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>JA oder NEIN</t>
+          <t>Freitext</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Dauer letzte Stufe (min)</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>1.75</v>
+          <t>Letzte Stufe vollständig absolviert</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Nur ausfüllen wenn NEIN oben</t>
+          <t>JA oder NEIN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Ausbelastung</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
+          <t>Dauer letzte Stufe (min)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1.75</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>JA oder NEIN</t>
+          <t>Nur ausfüllen wenn NEIN oben</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Nachbelastungslaktat 3min (mmol/l)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
+          <t>Ausbelastung</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Optional — Laktatwert 3 min nach Belastung</t>
+          <t>JA oder NEIN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Nachbelastungslaktat 5min (mmol/l)</t>
+          <t>Nachbelastungslaktat 3min (mmol/l)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Optional — Laktatwert 3 min nach Belastung</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Nachbelastungslaktat 5min (mmol/l)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Optional — Laktatwert 5 min nach Belastung</t>
         </is>
@@ -956,7 +956,7 @@
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>RPE-Skala: 6-20 (Borg). 6=keine, 20=maximale Belastung</t>
+          <t>RPE-Skala: 0-10 (Borg CR10). 0 = keine Anstrengung, 10 = maximale Anstrengung</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         <v>1.9</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -991,7 +991,7 @@
         <v>2.8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1008,7 +1008,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1025,7 +1025,7 @@
         <v>3.8</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1042,7 +1042,7 @@
         <v>5.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1059,7 +1059,7 @@
         <v>7.9</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/templates/input_template.xlsx
+++ b/templates/input_template.xlsx
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -904,6 +904,36 @@
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Optional — Laktatwert 5 min nach Belastung</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Ruhelaktat (mmol/l)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Optional — Laktat vor Testbeginn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Steigung (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Optional — Laufband-/Strecken-Steigung in Prozent</t>
         </is>
       </c>
     </row>

--- a/templates/input_template.xlsx
+++ b/templates/input_template.xlsx
@@ -821,14 +821,10 @@
           <t>Besonderheiten</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>1% Steigung</t>
-        </is>
-      </c>
+      <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Freitext</t>
+          <t>Freitext (z.B. Witterung, Anreise)</t>
         </is>
       </c>
     </row>
